--- a/www/download/COUNTRY.DNK.rpA2.xlsx
+++ b/www/download/COUNTRY.DNK.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Dinamarca</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>5.59534474692871</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>5.79710144928534</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>6.59587093480106</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>6.69075326805805</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>6.96718477441534</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>8.05866701654832</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>8.31600818352559</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>7.8696784336552</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>6.5754865977623</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>5.98515681095156</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>5.98658985658789</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>5.94106463603802</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>5.4359641756125</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.07318051311202</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.34659312671883</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.553</t>
+          <t>1.26079293874031</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.584</t>
+          <t>1.29283551577984</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>1.86649830584443</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.668</t>
+          <t>1.65667372376074</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.694</t>
+          <t>1.62404777748676</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>1.6958722723801</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.742</t>
+          <t>1.56283698167874</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.746</t>
+          <t>1.44624570777439</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.714</t>
+          <t>1.13542851212212</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.698</t>
+          <t>1.10053324406004</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.727</t>
+          <t>1.14419725535567</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.783</t>
+          <t>1.13814356145721</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.861</t>
+          <t>1.1225166793448</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.907</t>
+          <t>1.23756764566684</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.856</t>
+          <t>1.41286548883676</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.352</t>
+          <t>0.0993646294947053</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.386</t>
+          <t>0.110372604566193</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.434</t>
+          <t>0.370250706400908</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.478</t>
+          <t>0.291598665269709</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.504</t>
+          <t>0.28349864977321</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.527</t>
+          <t>0.339672297633988</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.561</t>
+          <t>0.280560530770132</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.215525895273565</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>0.0493185405962546</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.524</t>
+          <t>0.035661294569614</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.554</t>
+          <t>0.034863375141583</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.0239106421602557</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.688</t>
+          <t>0.0263555074933579</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>0.078649178182846</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.651</t>
+          <t>0.178603095320906</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3946.525</t>
+          <t>-0.440128440267252</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3968.857</t>
+          <t>-0.435180917662957</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4069.596</t>
+          <t>-0.310342320571833</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4172.171</t>
+          <t>-0.344952562841864</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4237.91</t>
+          <t>-0.345165130944585</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4300.641</t>
+          <t>-0.310665521875992</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4354.175</t>
+          <t>-0.338037678881268</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4335.214</t>
+          <t>-0.374507510388696</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4278.018</t>
+          <t>-0.434570017938373</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4260.686</t>
+          <t>-0.434693538284225</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>4305.218</t>
+          <t>-0.44483500140711</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4413.431</t>
+          <t>-0.429869059463291</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>4490.221</t>
+          <t>-0.473499726821438</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>4563.611</t>
+          <t>-0.447456776025768</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>4426.213</t>
+          <t>-0.399879659209414</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3561.707</t>
+          <t>17027117103.928</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3580.474</t>
+          <t>17043019531.3554</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3694.916</t>
+          <t>18178186349.0494</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3793.961</t>
+          <t>16985908731.4335</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3866.816</t>
+          <t>16263059225.9706</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3914.097</t>
+          <t>16625209036.4842</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3978.711</t>
+          <t>17123899809.9503</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3945.645</t>
+          <t>17013866198.3864</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3897.167</t>
+          <t>18048684353.5477</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3895.572</t>
+          <t>18577044829.3535</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3953.214</t>
+          <t>18415196454.1487</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4060.536</t>
+          <t>18938855296.135</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4152.28</t>
+          <t>18827473386.2678</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4239.784</t>
+          <t>18074062275.4081</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4075.162</t>
+          <t>15821518849.3864</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>8143056898.80057</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>8119423954.48557</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>6799066571.39832</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>7452301208.02992</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>7670369846.80436</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>7480932587.41995</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>7985504996.31648</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>8364973619.61368</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>9480488734.07139</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>9612874529.08307</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>31.33</t>
+          <t>9716907335.05728</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>10022078066.0314</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>10203759236.8242</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>9978218248.39839</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>8803117855.62635</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>55.06</t>
+          <t>2158423.76403634</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.35</t>
+          <t>2132501.83967435</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>2503548.38404822</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>2312758.75730406</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>2229730.25823153</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>55.47</t>
+          <t>2370153.13943201</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>55.35</t>
+          <t>2473587.61528472</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>2281447.76736749</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>2035384.68257457</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>51.69</t>
+          <t>1866086.01543016</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>49.78</t>
+          <t>1742984.19415581</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>1617442.07856164</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>46.69</t>
+          <t>1395825.79866158</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>1213034.61973092</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>45.08</t>
+          <t>1253929.61904411</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>29940.5846424663</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>29925.7904269252</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30414.8336803129</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>31026.7459874682</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>32634.371689843</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>33257.5674385673</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>32439.9175167127</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>33025.4577845763</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>35353.1916248247</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>38365.5135647049</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>41615.1148277926</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>44308.5845483727</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>47247.0878264729</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>54020.8155997354</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>48806.7103837883</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>74274.8274381842</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>74117.1636773374</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>77750.5870131175</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.52</t>
+          <t>71755.5835959861</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>41.99</t>
+          <t>70882.5436045193</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>72874.3000901089</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>72407.3182993154</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>72866.9117189641</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>82760.693069546</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>92390.2021819214</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>50.13</t>
+          <t>97415.9718465329</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>104272.330519276</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>48.27</t>
+          <t>116205.608538753</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>51.23</t>
+          <t>121863.186511018</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>51.79</t>
+          <t>98600.5083699256</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>50.87</t>
+          <t>0.350311772755886</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>0.375662274440565</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>0.719623073784208</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49.54</t>
+          <t>0.623247812150844</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>49.41</t>
+          <t>0.623098865025758</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>0.69553925406173</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>48.92</t>
+          <t>0.629278357328959</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>48.38</t>
+          <t>0.56529310554358</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>0.39103372734961</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>0.381744117412144</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>0.398842128100096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>0.405254806478792</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>0.33451766091841</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>0.434384869546108</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>0.548499270146898</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>43861.1988105663</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>42639.5074734847</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>37539.4074308078</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>37095.3679527012</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>36258.1552354508</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>32077.3538309134</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>31029.8023038557</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>32682.0896666281</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>38628.7880709085</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>43816.496792744</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>43196.1392134982</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>44064.2666732117</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>49859.7500613318</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.59534474692871</t>
+          <t>3461.90292318973</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5.79710144928534</t>
+          <t>3403.34463299558</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6.59587093480106</t>
+          <t>2793.43935263768</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6.69075326805805</t>
+          <t>3007.81759123987</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6.96718477441534</t>
+          <t>3063.33115681078</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.05866701654832</t>
+          <t>2960.16525294979</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.31600818352559</t>
+          <t>3118.57164638707</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.8696784336552</t>
+          <t>3268.05547531455</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6.5754865977623</t>
+          <t>3747.06731372893</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5.98515681095156</t>
+          <t>3809.31633473564</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5.98658985658789</t>
+          <t>3804.85803795468</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>5.94106463603802</t>
+          <t>3839.20589584018</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>5.4359641756125</t>
+          <t>3796.29983619575</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>5.07318051311202</t>
+          <t>3651.32846987648</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5.34659312671883</t>
+          <t>3321.20723492875</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>8912480775.70392</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>9090183598.41176</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>7433209987.76951</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>7198535493.6011</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>8467794198.54497</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>8723363632.26436</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>9444377144.94338</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>9752289003.56731</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>11729437564.6965</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>11878685955.7756</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>12117164118.7799</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>11744783802.0885</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>11680763561.5006</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>12306144461.8983</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>10576655875.6979</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>10309233371.3601</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>10452047666.8332</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>8681732319.68847</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>8521908362.42569</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>9939116475.77176</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>10964076903.8644</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>11936042635.1979</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>12391742867.1592</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>14507762858.9556</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>15137066590.4266</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>15509596344.8352</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>15305923633.8498</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>15771755667.1749</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>16608832727.7173</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>14812467116.4506</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>-1396752595.65616</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-1361864068.42143</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>-1248522331.91896</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>-1323372868.82458</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>-1471322277.22679</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>-2240713271.60004</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>-2491665490.25454</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-2639453863.59191</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>-2778325294.25917</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>-3258380634.65098</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>-3392432226.05531</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>-3561139831.76131</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>-4090992105.6743</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4302688265.81895</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4235811240.75273</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>4674.64827332111</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>4681.85281853178</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>4803.66276601258</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>4882.43332432894</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>4972.08932381761</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>5019.07638488593</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>5081.0212892382</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>5115.46470404381</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>5212.29701204625</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>5263.50043688296</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>5322.39571493129</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>5395.06253819113</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>5066.22917754489</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>5237.41031093377</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>5142.88697929377</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>4702.24968007418</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>4722.83413050351</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>4833.57947428831</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>4918.82966525728</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>5001.78857513174</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>5071.29735738609</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>5130.28211281304</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>5175.31567122656</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>5271.17323346021</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>5319.0228777846</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>5364.70154148921</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>5440.32293628784</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>5096.16802082014</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>5254.71410067026</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>5139.18117277844</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>126.08</t>
+          <t>63435.7198688412</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>64834.8321353354</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>186.65</t>
+          <t>59901.0402145433</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>165.67</t>
+          <t>59002.918688465</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>63789.1418136659</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>169.59</t>
+          <t>68026.8757360042</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>156.28</t>
+          <t>68753.7176463007</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>144.62</t>
+          <t>72415.7853827395</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>113.54</t>
+          <t>85723.8896220672</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>110.05</t>
+          <t>98085.0182609527</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>114.42</t>
+          <t>112538.837149356</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>113.81</t>
+          <t>128101.820149994</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>112.25</t>
+          <t>147311.572262702</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>123.76</t>
+          <t>172483.935431814</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>141.29</t>
+          <t>133160.800462652</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>5949249153.03198</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>6059434050.48158</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>6453495658.75777</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>5742838078.09728</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>5739332368.0531</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>5861429590.47901</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>6159697718.15816</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>6011806587.64814</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>6410977290.99043</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>6574899944.04156</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>6444563187.93058</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>6912168494.43664</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>6796821280.08666</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>6770549923.32923</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>5613529915.69039</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-44.01</t>
+          <t>53811.4976921497</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-43.52</t>
+          <t>53513.5597832022</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-31.03</t>
+          <t>50842.6571843734</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-34.5</t>
+          <t>52477.1155841272</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-34.52</t>
+          <t>52539.4291892659</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-31.07</t>
+          <t>56304.4997621318</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-33.8</t>
+          <t>56392.820255366</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-37.45</t>
+          <t>60285.701819875</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-43.46</t>
+          <t>69948.6046646054</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-43.47</t>
+          <t>83296.9080151088</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-44.48</t>
+          <t>96932.128610976</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-42.99</t>
+          <t>115795.462744549</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-47.35</t>
+          <t>135452.41609655</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-44.75</t>
+          <t>156527.12150155</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-39.99</t>
+          <t>117439.956803008</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12003.546</t>
+          <t>12094020764.0811</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>12204.351</t>
+          <t>11963139578.3084</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12701.598</t>
+          <t>11515352314.8082</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>13123.959</t>
+          <t>11123259039.3319</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>13473.403</t>
+          <t>10952246174.4032</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>13755.874</t>
+          <t>11119364259.172</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14069.67</t>
+          <t>11732750471.9321</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14211.21</t>
+          <t>11971732531.8573</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>14303.534</t>
+          <t>13469470724.3073</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>14348.82</t>
+          <t>14393852096.7102</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>14629.069</t>
+          <t>14571371796.5234</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>15142.889</t>
+          <t>15765185240.4484</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>14579.112</t>
+          <t>16003564263.0202</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>15277.975</t>
+          <t>16065908008.6019</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>14679.774</t>
+          <t>12882334796.4572</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10995.666</t>
+          <t>9624.22217669158</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11169.585</t>
+          <t>11321.2723521332</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11691.832</t>
+          <t>9058.38303016988</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>12096.932</t>
+          <t>6525.8031043378</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>12449.769</t>
+          <t>11249.7126244</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12684.215</t>
+          <t>11722.3759738724</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13010.61</t>
+          <t>12360.8973909347</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13093.636</t>
+          <t>12130.0835628645</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>13187.68</t>
+          <t>15775.2849574618</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>13282.533</t>
+          <t>14788.1102458439</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>13592.419</t>
+          <t>15606.7085383796</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>14083.573</t>
+          <t>12306.3574054449</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>13617.097</t>
+          <t>11859.1561661517</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>14312.605</t>
+          <t>15956.8139302642</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>13631.622</t>
+          <t>15720.8436596438</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17027.117</t>
+          <t>-6144771611.04907</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>17043.02</t>
+          <t>-5903705527.82684</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18178.186</t>
+          <t>-5061856656.05039</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>16985.909</t>
+          <t>-5380420961.23467</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>16263.059</t>
+          <t>-5212913806.35012</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>16625.209</t>
+          <t>-5257934668.69302</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17123.9</t>
+          <t>-5573052753.77397</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>17013.866</t>
+          <t>-5959925944.20918</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18048.684</t>
+          <t>-7058493433.31685</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>18577.045</t>
+          <t>-7818952152.66868</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>18415.196</t>
+          <t>-8126808608.59286</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>18938.855</t>
+          <t>-8853016746.01178</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>18827.473</t>
+          <t>-9206742982.93355</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>18074.062</t>
+          <t>-9295358085.27265</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>15821.519</t>
+          <t>-7268804880.76685</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>76158.1308</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>77336.40736</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>71561.74027</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71798.34376</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>72001.2481</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>68338.96983</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>67699.42724</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72464.58774</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>87710.6187</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>100475.73005</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>105203.46576</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>110691.77672</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>123787.42364</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>137405.3237</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>120509.42214</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6863.723</t>
+          <t>0.0139811336534613</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6881.346</t>
+          <t>0.0145448918318697</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7111.027</t>
+          <t>0.0187305684590437</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>7344.62</t>
+          <t>0.0156126010177232</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7487.524</t>
+          <t>0.0173309104275905</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7587.229</t>
+          <t>0.0260410905227444</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7671.847</t>
+          <t>0.02530057128917</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>7711.192</t>
+          <t>0.0249311535070664</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>7709.923</t>
+          <t>0.026484276164611</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>7714.215</t>
+          <t>0.0306657645992037</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>7866.785</t>
+          <t>0.0339216693411881</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>8047.714</t>
+          <t>0.0368486967378255</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>7654.908</t>
+          <t>0.0334409342916807</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>8012.063</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>7831.565</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>94971.4486076223</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>96628.980039683</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>89063.7497972945</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>92950.5213038583</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>93612.2728596442</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>84412.844093664</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>86209.8718097497</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>94381.1111311811</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>115950.35382168</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>131238.165489814</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>137583.502637156</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>146652.503161933</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>170947.778596475</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>192843.389463581</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>184367.104605978</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>8143.057</t>
+          <t>103620.007425453</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8119.424</t>
+          <t>105475.073243332</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6799.067</t>
+          <t>96758.6284176353</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>7452.301</t>
+          <t>100831.035595434</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>7670.37</t>
+          <t>101218.949515811</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7480.933</t>
+          <t>91433.6251083937</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>7985.505</t>
+          <t>93025.9601306236</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8364.974</t>
+          <t>102246.71517741</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>9480.489</t>
+          <t>125590.118048088</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>9612.875</t>
+          <t>141688.54413748</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>9716.907</t>
+          <t>148070.084821056</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>10022.078</t>
+          <t>157652.834543269</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>10203.759</t>
+          <t>182898.0467475</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>9978.218</t>
+          <t>206255.911435343</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>8803.118</t>
+          <t>196642.801807363</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>35.03</t>
+          <t>715381.910500846</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>37.57</t>
+          <t>709772.477686175</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>71.96</t>
+          <t>632367.628214615</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>631824.896483757</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>617201.332464887</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>69.55</t>
+          <t>550681.842535283</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>62.93</t>
+          <t>545429.626777945</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>56.53</t>
+          <t>579962.246506701</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>696232.369591542</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>776989.753922345</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>39.88</t>
+          <t>806714.107145036</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>40.53</t>
+          <t>826951.669697429</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>937322.41144249</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.158</t>
+          <t>103620.007425453</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.133</t>
+          <t>107478.314061647</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.504</t>
+          <t>110091.980918479</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.313</t>
+          <t>115257.242471884</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>118907.260944611</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>122273.834383458</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.474</t>
+          <t>124968.864195211</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.281</t>
+          <t>127043.999053328</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.035</t>
+          <t>128545.372161906</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.866</t>
+          <t>129168.433981206</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.743</t>
+          <t>134200.158010163</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>139609.194989764</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>146197.708638013</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.213</t>
+          <t>148501.834772705</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.254</t>
+          <t>146718.272109112</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>94971.4486076223</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>98437.1041364147</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>101225.25690119</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>105795.945888027</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>109542.071798057</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>112637.152021985</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>115656.904164777</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>116820.83945849</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>118078.377225152</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>119057.522886082</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>123814.229867481</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>129272.648164632</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>136062.616394368</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>137805.029282041</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>135438.121692759</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>53863.0489145471</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>52963.0713866682</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>49384.0125823647</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>46959.7979745664</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>46954.8162441893</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>46417.7095416063</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>44829.4834593764</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>47141.2174625898</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>57067.9984219124</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>67643.4816825199</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>70561.2284089439</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>74536.3579667307</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>81204.6872324998</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>88539.9696946574</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>71286.3013226369</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>10995665596.6714</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>11169585224.3748</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>11691831756.3714</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>12096931631.4237</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>12449768592.676</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>12684214858.9601</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>13010610462.8407</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>13093635534.8352</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>13187679580.8513</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>13282532831.9816</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>13592419335.123</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>14083573373.1963</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>13617096909.3012</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>14312605280.5315</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>13631621574.4545</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>12003545612.3177</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>12204351241.9802</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>12701597971.6838</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>13123958942.8509</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>13473402915.2382</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>13755873796.7203</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>14069670437.3369</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>14211209820.5613</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>14303534144.7504</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>14348819514.0726</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>14629069009.9054</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>15142888638.3021</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>14579112377.7942</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>15277974966.177</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>14679773639.505</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>6863722992.71416</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>6881345769.75569</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>7111026882.95835</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>7344619737.80094</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>7487523621.54814</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>7587229105.83669</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7671847410.54679</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>7711191631.86663</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>7709923308.5295</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>7714214803.74415</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>7866785091.69985</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>8047713779.47736</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>7654908397.42842</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>8012063472.75087</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>7831564979.52882</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2552724</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2584116</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2627783</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2668106</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2693717</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2712496</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2742475</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2745960</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2713539</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2697642</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2726912</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2783454</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2860799</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2907479.77406196</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2856442.13464624</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2352191</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2385719</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2433941</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2477644</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2503931</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2527201</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2560629</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2559618</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2530109</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2523517</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2553816</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2610456</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2687817</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2732763.79562092</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2650577.70651737</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3946525000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3968857000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4069596000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4172171000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>4237910000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>4300641000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4354175000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>4335214000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>4278018000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>4260686000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>4305218000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>4413431000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>4490221000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>4563611344.86316</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>4426213429.23584</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3561707000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3580474000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3694916000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3793961000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3866816000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3914097000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3978711000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3945645000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3897167000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3895572000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3953214000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4060536000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4152280000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>4239783579</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4075161790.5794</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.223883473903054</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.23009214177032</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.236057132689494</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.245884667325644</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.250745961750358</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.255718720169047</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.263689990284609</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.268654797798724</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.299574972719611</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.302815111287093</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.313331495645102</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.318690099132054</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.289584372171691</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.310858210514823</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.312893410037268</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.550590716553441</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.553503630601798</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.553976662936635</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.553250491018004</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.554990553961462</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.554732294142613</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.553521750790115</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.552981915247363</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.521002579797404</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.516869446873403</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.497784424326814</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.501836405989754</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.466878590140647</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.466304492760894</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.450798377646792</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.225525809543505</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.216404227627882</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.209966204373871</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.200864841656351</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.19426348428818</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.18954898568834</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.182788258925276</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.178363286953914</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.179422447482985</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.180315441839504</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.188884080028084</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.179473494878193</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.243537037687662</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.222837296724283</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.236308212315941</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.386812349325059</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.39679394129873</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.405783630873547</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.415204080436876</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.419883812692644</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.420257997596477</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.429898166099418</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.43899239834013</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.481020905048913</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.4850804102428</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.501317782629348</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.506985826067859</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.4826845310024</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.51232996429474</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.517862916599619</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.508675782751281</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.504606716269431</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.500097814082655</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.495415494514964</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.494145247981435</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.495230087293385</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.489226498135873</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.483832875522457</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.440663807425436</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.436008486739805</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.418101348065121</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.413438054075713</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.409629058751028</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.392109697756292</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.381033434375838</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.10451186792366</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.098599342431839</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0941185550437974</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0893804250481609</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0859709393259211</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0845119151101382</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0808753357647092</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0771747261374131</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0783152875256509</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0789111030173959</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0805808693055305</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0795761198564279</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.107686410246572</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0955603379489685</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.101103649024543</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>298365.88747</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>300756.85585</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>278356.72166</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>283172.60081</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>285252.09168</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>269250.11318</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>273930.34712</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>295493.52028</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>357987.64963</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>410428.67847</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>444056.31049</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>484097.74638</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>561740.27321</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>630254.4631</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>549075.19184</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>157483.05634</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>158438.14463</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>146142.641</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>147790.83357</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>148173.76576</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>137851.33465</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>137855.44359</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>149387.93264</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>182658.11647</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>209332.02582</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>218631.31323</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>232189.19251</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>264102.73398</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>294795.88113</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>267929.10313</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4002808.50525748</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4051529.22530515</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>4122038.58445243</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4209363.92366684</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4297531.14459968</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4392592.39584807</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4488085.90693917</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4589482.40146926</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>4676428.29878684</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>4777350.63208677</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>4898627.25363918</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>5080876.73712512</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>5275543.10240717</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
